--- a/Healthcare_OnCall_Dashboard.xlsx
+++ b/Healthcare_OnCall_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keonalollis/Documents/healthcare-operations-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8694244-66D6-EF42-B6D8-7C8EC6AC324C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F549B1-1758-B840-BCD5-1317D1359F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16240" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16240" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Providers" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="58" r:id="rId9"/>
-    <pivotCache cacheId="66" r:id="rId10"/>
+    <pivotCache cacheId="67" r:id="rId9"/>
+    <pivotCache cacheId="68" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9176" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9177" uniqueCount="1498">
   <si>
     <t>Provider ID</t>
   </si>
@@ -4082,9 +4082,6 @@
     <t>Shifts</t>
   </si>
   <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
     <t>Grand Total</t>
   </si>
   <si>
@@ -4094,9 +4091,6 @@
     <t>Total Shifts</t>
   </si>
   <si>
-    <t>Column Labels</t>
-  </si>
-  <si>
     <t>Jun</t>
   </si>
   <si>
@@ -4554,6 +4548,18 @@
   </si>
   <si>
     <t>johnsonjean@example.net</t>
+  </si>
+  <si>
+    <t>Assigned Shifts</t>
+  </si>
+  <si>
+    <t>Department Coverage Report</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Providers Per Department</t>
   </si>
 </sst>
 </file>
@@ -4567,7 +4573,7 @@
     <numFmt numFmtId="167" formatCode="h:mm;@"/>
     <numFmt numFmtId="168" formatCode="[&lt;=9999999]###\-####;\(###\)\ ###\-####"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4604,8 +4610,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4630,8 +4642,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -4650,29 +4668,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22561,7 +22674,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09BF837F-C911-8943-89A3-9EA4A308B762}" name="PivotTable2" cacheId="66" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09BF837F-C911-8943-89A3-9EA4A308B762}" name="PivotTable2" cacheId="68" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Provider ID">
   <location ref="A3:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -23825,7 +23938,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total Shifts" fld="9" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Assigned Shifts" fld="9" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -23840,7 +23953,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C16D6B02-F3CF-F343-9BCF-090CE3B17761}" name="PivotTable3" cacheId="66" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C16D6B02-F3CF-F343-9BCF-090CE3B17761}" name="PivotTable3" cacheId="68" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department" colHeaderCaption="Month">
   <location ref="A3:E15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -24961,7 +25074,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Provider ID" fld="9" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Assigned Shifts" fld="9" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -24976,7 +25089,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{307DCAFB-B345-1E4D-80DD-9E7331CC328D}" name="PivotTable4" cacheId="66" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Schedule Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{307DCAFB-B345-1E4D-80DD-9E7331CC328D}" name="PivotTable4" cacheId="68" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Schedule Status">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -25324,7 +25437,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6B154A-8779-4148-91BB-19C445CC0B9E}" name="PivotTable5" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6B154A-8779-4148-91BB-19C445CC0B9E}" name="PivotTable5" cacheId="67" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Provider Level" colHeaderCaption="Providers Per Department">
   <location ref="A3:E15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField dataField="1" showAll="0"/>
@@ -25778,43 +25891,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -25823,7 +25936,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
@@ -25850,13 +25963,13 @@
         <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="L2">
         <v>9143</v>
       </c>
       <c r="M2" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -25864,7 +25977,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
@@ -25891,13 +26004,13 @@
         <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="L3">
         <v>2222</v>
       </c>
       <c r="M3" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -25905,7 +26018,7 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
@@ -25932,13 +26045,13 @@
         <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="L4">
         <v>5343</v>
       </c>
       <c r="M4" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -25946,7 +26059,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
@@ -25973,13 +26086,13 @@
         <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="L5">
         <v>3178</v>
       </c>
       <c r="M5" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -25987,7 +26100,7 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -26014,13 +26127,13 @@
         <v>18</v>
       </c>
       <c r="K6" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="L6">
         <v>2889</v>
       </c>
       <c r="M6" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -26028,7 +26141,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
@@ -26055,13 +26168,13 @@
         <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="L7">
         <v>1459</v>
       </c>
       <c r="M7" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -26069,7 +26182,7 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
@@ -26096,13 +26209,13 @@
         <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="L8">
         <v>4673</v>
       </c>
       <c r="M8" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -26110,7 +26223,7 @@
         <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -26137,13 +26250,13 @@
         <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="L9">
         <v>2455</v>
       </c>
       <c r="M9" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -26151,7 +26264,7 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
@@ -26178,13 +26291,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="L10">
         <v>8718</v>
       </c>
       <c r="M10" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -26192,7 +26305,7 @@
         <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
@@ -26219,13 +26332,13 @@
         <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="L11">
         <v>9333</v>
       </c>
       <c r="M11" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -26233,7 +26346,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
@@ -26260,13 +26373,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="L12">
         <v>3171</v>
       </c>
       <c r="M12" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -26274,7 +26387,7 @@
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
@@ -26301,13 +26414,13 @@
         <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="L13">
         <v>3250</v>
       </c>
       <c r="M13" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -26315,7 +26428,7 @@
         <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
@@ -26342,13 +26455,13 @@
         <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="L14">
         <v>9693</v>
       </c>
       <c r="M14" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -26356,7 +26469,7 @@
         <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
@@ -26383,13 +26496,13 @@
         <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="L15">
         <v>5292</v>
       </c>
       <c r="M15" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -26397,7 +26510,7 @@
         <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
@@ -26424,13 +26537,13 @@
         <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="L16">
         <v>3982</v>
       </c>
       <c r="M16" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -26438,7 +26551,7 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -26465,13 +26578,13 @@
         <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="L17">
         <v>1225</v>
       </c>
       <c r="M17" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -26479,7 +26592,7 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -26506,13 +26619,13 @@
         <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="L18">
         <v>2338</v>
       </c>
       <c r="M18" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -26520,7 +26633,7 @@
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -26547,13 +26660,13 @@
         <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="L19">
         <v>9037</v>
       </c>
       <c r="M19" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -26561,7 +26674,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -26588,13 +26701,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="L20">
         <v>8914</v>
       </c>
       <c r="M20" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
@@ -26602,7 +26715,7 @@
         <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -26629,13 +26742,13 @@
         <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="L21">
         <v>6630</v>
       </c>
       <c r="M21" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -26643,7 +26756,7 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
@@ -26670,13 +26783,13 @@
         <v>18</v>
       </c>
       <c r="K22" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="L22">
         <v>6789</v>
       </c>
       <c r="M22" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
@@ -26684,7 +26797,7 @@
         <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
@@ -26711,13 +26824,13 @@
         <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="L23">
         <v>3268</v>
       </c>
       <c r="M23" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
@@ -26725,7 +26838,7 @@
         <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -26752,13 +26865,13 @@
         <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="L24">
         <v>1471</v>
       </c>
       <c r="M24" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
@@ -26766,7 +26879,7 @@
         <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="C25" t="s">
         <v>38</v>
@@ -26793,13 +26906,13 @@
         <v>34</v>
       </c>
       <c r="K25" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="L25">
         <v>5421</v>
       </c>
       <c r="M25" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
@@ -26807,7 +26920,7 @@
         <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="C26" t="s">
         <v>38</v>
@@ -26834,13 +26947,13 @@
         <v>18</v>
       </c>
       <c r="K26" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="L26">
         <v>9424</v>
       </c>
       <c r="M26" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
@@ -26848,7 +26961,7 @@
         <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="C27" t="s">
         <v>29</v>
@@ -26875,13 +26988,13 @@
         <v>18</v>
       </c>
       <c r="K27" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="L27">
         <v>9390</v>
       </c>
       <c r="M27" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
@@ -26889,7 +27002,7 @@
         <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="C28" t="s">
         <v>29</v>
@@ -26916,13 +27029,13 @@
         <v>18</v>
       </c>
       <c r="K28" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="L28">
         <v>5739</v>
       </c>
       <c r="M28" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
@@ -26930,7 +27043,7 @@
         <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="C29" t="s">
         <v>29</v>
@@ -26957,13 +27070,13 @@
         <v>18</v>
       </c>
       <c r="K29" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="L29">
         <v>7491</v>
       </c>
       <c r="M29" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
@@ -26971,7 +27084,7 @@
         <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="C30" t="s">
         <v>29</v>
@@ -26998,13 +27111,13 @@
         <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="L30">
         <v>9120</v>
       </c>
       <c r="M30" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
@@ -27012,7 +27125,7 @@
         <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -27039,13 +27152,13 @@
         <v>18</v>
       </c>
       <c r="K31" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="L31">
         <v>1233</v>
       </c>
       <c r="M31" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
@@ -27053,7 +27166,7 @@
         <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="C32" t="s">
         <v>20</v>
@@ -27080,13 +27193,13 @@
         <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="L32">
         <v>2320</v>
       </c>
       <c r="M32" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -27094,7 +27207,7 @@
         <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
@@ -27121,13 +27234,13 @@
         <v>18</v>
       </c>
       <c r="K33" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="L33">
         <v>9213</v>
       </c>
       <c r="M33" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -27135,7 +27248,7 @@
         <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="C34" t="s">
         <v>20</v>
@@ -27162,13 +27275,13 @@
         <v>18</v>
       </c>
       <c r="K34" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="L34">
         <v>7673</v>
       </c>
       <c r="M34" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -27176,7 +27289,7 @@
         <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
@@ -27203,13 +27316,13 @@
         <v>18</v>
       </c>
       <c r="K35" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="L35">
         <v>3071</v>
       </c>
       <c r="M35" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -27217,7 +27330,7 @@
         <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
@@ -27244,13 +27357,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="L36">
         <v>8733</v>
       </c>
       <c r="M36" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -27258,7 +27371,7 @@
         <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="C37" t="s">
         <v>72</v>
@@ -27285,13 +27398,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="L37">
         <v>7223</v>
       </c>
       <c r="M37" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
@@ -27299,7 +27412,7 @@
         <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="C38" t="s">
         <v>72</v>
@@ -27326,13 +27439,13 @@
         <v>18</v>
       </c>
       <c r="K38" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="L38">
         <v>2638</v>
       </c>
       <c r="M38" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
@@ -27340,7 +27453,7 @@
         <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="C39" t="s">
         <v>72</v>
@@ -27367,13 +27480,13 @@
         <v>18</v>
       </c>
       <c r="K39" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="L39">
         <v>4215</v>
       </c>
       <c r="M39" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
@@ -27381,7 +27494,7 @@
         <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="C40" t="s">
         <v>72</v>
@@ -27408,13 +27521,13 @@
         <v>24</v>
       </c>
       <c r="K40" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="L40">
         <v>5427</v>
       </c>
       <c r="M40" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
@@ -27422,7 +27535,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C41" t="s">
         <v>72</v>
@@ -27449,13 +27562,13 @@
         <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="L41">
         <v>1914</v>
       </c>
       <c r="M41" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
@@ -27463,7 +27576,7 @@
         <v>79</v>
       </c>
       <c r="B42" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C42" t="s">
         <v>56</v>
@@ -27490,13 +27603,13 @@
         <v>18</v>
       </c>
       <c r="K42" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="L42">
         <v>9284</v>
       </c>
       <c r="M42" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
@@ -27504,7 +27617,7 @@
         <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="C43" t="s">
         <v>56</v>
@@ -27531,13 +27644,13 @@
         <v>18</v>
       </c>
       <c r="K43" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="L43">
         <v>1809</v>
       </c>
       <c r="M43" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
@@ -27545,7 +27658,7 @@
         <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="C44" t="s">
         <v>56</v>
@@ -27572,13 +27685,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="L44">
         <v>2496</v>
       </c>
       <c r="M44" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
@@ -27586,7 +27699,7 @@
         <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="C45" t="s">
         <v>56</v>
@@ -27613,13 +27726,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="L45">
         <v>8420</v>
       </c>
       <c r="M45" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
@@ -27627,7 +27740,7 @@
         <v>83</v>
       </c>
       <c r="B46" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C46" t="s">
         <v>56</v>
@@ -27654,13 +27767,13 @@
         <v>18</v>
       </c>
       <c r="K46" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="L46">
         <v>9206</v>
       </c>
       <c r="M46" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
@@ -27668,7 +27781,7 @@
         <v>84</v>
       </c>
       <c r="B47" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="C47" t="s">
         <v>50</v>
@@ -27695,13 +27808,13 @@
         <v>18</v>
       </c>
       <c r="K47" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="L47">
         <v>3884</v>
       </c>
       <c r="M47" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
@@ -27709,7 +27822,7 @@
         <v>85</v>
       </c>
       <c r="B48" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="C48" t="s">
         <v>50</v>
@@ -27736,13 +27849,13 @@
         <v>18</v>
       </c>
       <c r="K48" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="L48">
         <v>8964</v>
       </c>
       <c r="M48" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -27750,7 +27863,7 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C49" t="s">
         <v>50</v>
@@ -27777,13 +27890,13 @@
         <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="L49">
         <v>7239</v>
       </c>
       <c r="M49" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
@@ -27791,7 +27904,7 @@
         <v>87</v>
       </c>
       <c r="B50" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="C50" t="s">
         <v>50</v>
@@ -27818,13 +27931,13 @@
         <v>18</v>
       </c>
       <c r="K50" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="L50">
         <v>9426</v>
       </c>
       <c r="M50" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
@@ -27832,7 +27945,7 @@
         <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="C51" t="s">
         <v>50</v>
@@ -27859,13 +27972,13 @@
         <v>18</v>
       </c>
       <c r="K51" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="L51">
         <v>7062</v>
       </c>
       <c r="M51" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
   </sheetData>
@@ -70647,153 +70760,249 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>1331</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
       <c r="H2" s="9"/>
     </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+    </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="6">
-        <v>46200</v>
-      </c>
+      <c r="C4" s="14">
+        <v>46232</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
+      <c r="C5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="12"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
+      <c r="C6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="12"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="4"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="12"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="4"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C9" t="str" cm="1">
+      <c r="C9" s="11" t="str" cm="1">
         <f t="array" ref="C9">_xlfn.XLOOKUP($C$4&amp;$C$5&amp;$C$6,tblSchedule[Date]&amp;tblSchedule[Department]&amp;tblSchedule[Shift],tblSchedule[Provider ID],"No Matching Assignment Foiund")</f>
-        <v>DR029</v>
-      </c>
+        <v>DR038</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" s="11" t="str">
         <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Provider Name],"NO PROVIDER FOUND")</f>
-        <v>Dr. Jordan Porter</v>
-      </c>
+        <v>Dr. Donna Fowler</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="13" t="s">
         <v>1334</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C11" s="11" t="str">
         <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Provider Level],"")</f>
-        <v>Fellow</v>
-      </c>
+        <v>Resident</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C12" s="11" t="str">
         <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Specialty],"")</f>
-        <v>General Surgery</v>
-      </c>
+        <v>Maternal-Fetal Medicine</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="8" t="str">
-        <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Phone Number],"")</f>
-        <v>001-846-427-3838</v>
-      </c>
+      <c r="C13" s="16" t="str">
+        <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Phone Number],"Not Found")</f>
+        <v>981-327-2699</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="11">
         <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Extension],"")</f>
-        <v>9120</v>
-      </c>
+        <v>4215</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="12"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="13" t="s">
         <v>1332</v>
       </c>
-      <c r="C15" s="7" cm="1">
+      <c r="C15" s="17" cm="1">
         <f t="array" ref="C15">_xlfn.XLOOKUP($C$4&amp;$C$5&amp;$C$6,tblSchedule[Date]&amp;tblSchedule[Department]&amp;tblSchedule[Shift],tblSchedule[Start Date/Time],"")</f>
-        <v>46200.791666666657</v>
-      </c>
+        <v>46232.291666666657</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="13" t="s">
         <v>1333</v>
       </c>
-      <c r="C16" s="7" cm="1">
+      <c r="C16" s="17" cm="1">
         <f t="array" ref="C16">_xlfn.XLOOKUP($C$4&amp;$C$5&amp;$C$6,tblSchedule[Date]&amp;tblSchedule[Department]&amp;tblSchedule[Shift],tblSchedule[End Date/Time],"")</f>
-        <v>46201.291666666657</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
+        <v>46232.791666666657</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C17" t="str" cm="1">
+      <c r="C17" s="11" t="str" cm="1">
         <f t="array" ref="C17">_xlfn.XLOOKUP($C$4&amp;$C$5&amp;$C$6,tblSchedule[Date]&amp;tblSchedule[Department]&amp;tblSchedule[Shift],tblSchedule[Schedule Status],"")</f>
-        <v>Completed</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
+        <v>Scheduled</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="11">
         <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Years of Experience],"")</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C19" s="11" t="str">
         <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Employment Type],"")</f>
-        <v>PRN</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
+        <v>Full-Time</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C20" s="19" t="str">
         <f>_xlfn.XLOOKUP($C$9,tblProviders[Provider ID],tblProviders[Shift Preference],"")</f>
         <v>Both</v>
       </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -70847,7 +71056,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" cm="1">
+      <c r="A2" s="3" cm="1">
         <f t="array" ref="A2:A62">_xlfn._xlws.SORT(_xlfn.UNIQUE(tblSchedule[Date]))</f>
         <v>46189</v>
       </c>
@@ -70861,7 +71070,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>46190</v>
       </c>
       <c r="B3" t="str">
@@ -70872,7 +71081,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <v>46191</v>
       </c>
       <c r="B4" t="str">
@@ -70880,7 +71089,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>46192</v>
       </c>
       <c r="B5" t="str">
@@ -70888,7 +71097,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>46193</v>
       </c>
       <c r="B6" t="str">
@@ -70896,7 +71105,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>46194</v>
       </c>
       <c r="B7" t="str">
@@ -70904,7 +71113,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>46195</v>
       </c>
       <c r="B8" t="str">
@@ -70912,7 +71121,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+      <c r="A9" s="3">
         <v>46196</v>
       </c>
       <c r="B9" t="str">
@@ -70920,7 +71129,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
+      <c r="A10" s="3">
         <v>46197</v>
       </c>
       <c r="B10" t="str">
@@ -70928,7 +71137,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>46198</v>
       </c>
       <c r="B11" t="str">
@@ -70936,257 +71145,257 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
+      <c r="A12" s="3">
         <v>46199</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
+      <c r="A13" s="3">
         <v>46200</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
+      <c r="A14" s="3">
         <v>46201</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
+      <c r="A15" s="3">
         <v>46202</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
+      <c r="A16" s="3">
         <v>46203</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
+      <c r="A17" s="3">
         <v>46204</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
+      <c r="A18" s="3">
         <v>46205</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
+      <c r="A19" s="3">
         <v>46206</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
+      <c r="A20" s="3">
         <v>46207</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
+      <c r="A21" s="3">
         <v>46208</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
+      <c r="A22" s="3">
         <v>46209</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
+      <c r="A23" s="3">
         <v>46210</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
+      <c r="A24" s="3">
         <v>46211</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
+      <c r="A25" s="3">
         <v>46212</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5">
+      <c r="A26" s="3">
         <v>46213</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5">
+      <c r="A27" s="3">
         <v>46214</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5">
+      <c r="A28" s="3">
         <v>46215</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5">
+      <c r="A29" s="3">
         <v>46216</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="5">
+      <c r="A30" s="3">
         <v>46217</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5">
+      <c r="A31" s="3">
         <v>46218</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5">
+      <c r="A32" s="3">
         <v>46219</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5">
+      <c r="A33" s="3">
         <v>46220</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="5">
+      <c r="A34" s="3">
         <v>46221</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5">
+      <c r="A35" s="3">
         <v>46222</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5">
+      <c r="A36" s="3">
         <v>46223</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5">
+      <c r="A37" s="3">
         <v>46224</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="5">
+      <c r="A38" s="3">
         <v>46225</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="5">
+      <c r="A39" s="3">
         <v>46226</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="5">
+      <c r="A40" s="3">
         <v>46227</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="5">
+      <c r="A41" s="3">
         <v>46228</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="5">
+      <c r="A42" s="3">
         <v>46229</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" s="5">
+      <c r="A43" s="3">
         <v>46230</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="5">
+      <c r="A44" s="3">
         <v>46231</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="5">
+      <c r="A45" s="3">
         <v>46232</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="5">
+      <c r="A46" s="3">
         <v>46233</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="5">
+      <c r="A47" s="3">
         <v>46234</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="5">
+      <c r="A48" s="3">
         <v>46235</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="5">
+      <c r="A49" s="3">
         <v>46236</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="5">
+      <c r="A50" s="3">
         <v>46237</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="5">
+      <c r="A51" s="3">
         <v>46238</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="5">
+      <c r="A52" s="3">
         <v>46239</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="5">
+      <c r="A53" s="3">
         <v>46240</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="5">
+      <c r="A54" s="3">
         <v>46241</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="5">
+      <c r="A55" s="3">
         <v>46242</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="5">
+      <c r="A56" s="3">
         <v>46243</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="5">
+      <c r="A57" s="3">
         <v>46244</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="5">
+      <c r="A58" s="3">
         <v>46245</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="5">
+      <c r="A59" s="3">
         <v>46246</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="5">
+      <c r="A60" s="3">
         <v>46247</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="5">
+      <c r="A61" s="3">
         <v>46248</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="5">
+      <c r="A62" s="3">
         <v>46249</v>
       </c>
     </row>
@@ -71200,391 +71409,391 @@
   <dimension ref="A3:B50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="22">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="22">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="22">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="22">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="22">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="22">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="22">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="22">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="22">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="22">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="22">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="22">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="22">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="22">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="22">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="22">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
         <v>1338</v>
       </c>
-      <c r="B3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="12">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="12">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="12">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="12">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="12">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="12">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="12">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="12">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="12">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="12">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="12">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="12">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B35" s="12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="12">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B38" s="12">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="12">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" s="12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43" s="12">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="12">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" s="12">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" s="12">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="12">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B48" s="12">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B49" s="12">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="11" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B50" s="12">
+      <c r="B50" s="22">
         <v>1220</v>
       </c>
     </row>
@@ -71595,7 +71804,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A301E3DF-7DD4-9448-A516-B08F9E97027B}">
-  <dimension ref="A3:E15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
@@ -71609,219 +71818,231 @@
     <col min="126" max="126" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>1340</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C4" t="s">
         <v>1342</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="D4" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E4" t="s">
         <v>1338</v>
       </c>
-      <c r="B4" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1344</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1339</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5">
         <v>30</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5">
         <v>62</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5">
         <v>30</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5">
         <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6">
         <v>30</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6">
         <v>62</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6">
         <v>30</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7">
         <v>30</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7">
         <v>62</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7">
         <v>30</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7">
         <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8">
         <v>30</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8">
         <v>62</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8">
         <v>30</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8">
         <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9">
         <v>30</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9">
         <v>62</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9">
         <v>30</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9">
         <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10">
         <v>30</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10">
         <v>62</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10">
         <v>30</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10">
         <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11">
         <v>30</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11">
         <v>62</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11">
         <v>30</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11">
         <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12">
         <v>30</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12">
         <v>62</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12">
         <v>30</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12">
         <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13">
         <v>30</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13">
         <v>62</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13">
         <v>30</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13">
         <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14">
         <v>30</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14">
         <v>62</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14">
         <v>30</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14">
         <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B15">
         <v>300</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15">
         <v>620</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15">
         <v>300</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15">
         <v>1220</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -71836,42 +72057,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5">
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6">
         <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B7">
         <v>1220</v>
       </c>
     </row>
@@ -71886,23 +72107,23 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
     <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>1340</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>1342</v>
+      <c r="A3" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1497</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>1338</v>
+      <c r="A4" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -71914,193 +72135,193 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9">
         <v>3</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11">
         <v>3</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12">
         <v>3</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14">
         <v>1</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14">
         <v>3</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B15">
         <v>10</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15">
         <v>10</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15">
         <v>30</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15">
         <v>50</v>
       </c>
     </row>
